--- a/ig/main/ValueSet-jdv-checklist-dlu-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-checklist-dlu-cisis.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085852</t>
+    <t>20260916095455</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:52+01:00</t>
+    <t>2026-09-16T09:54:55+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,36 +100,12 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>DLU_006</t>
-  </si>
-  <si>
-    <t>Attestation de la carte vitale</t>
-  </si>
-  <si>
-    <t>DLU_007</t>
-  </si>
-  <si>
-    <t>Attestation de mutuelle</t>
-  </si>
-  <si>
-    <t>DLU_008</t>
-  </si>
-  <si>
-    <t>Photocopie de la carte d’identité</t>
-  </si>
-  <si>
     <t>DLU_009</t>
   </si>
   <si>
     <t>Grille AGGIR (la plus récente)</t>
   </si>
   <si>
-    <t>DLU_010</t>
-  </si>
-  <si>
-    <t>Photocopie des directives anticipées</t>
-  </si>
-  <si>
     <t>DLU_011</t>
   </si>
   <si>
@@ -190,6 +167,33 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>ATTEST-DROITS-AM</t>
+  </si>
+  <si>
+    <t>Attestation de droits à l’assurance maladie</t>
+  </si>
+  <si>
+    <t>ATTEST-ASS-COMPL</t>
+  </si>
+  <si>
+    <t>Attestation assurance complémentaire</t>
+  </si>
+  <si>
+    <t>PIECE-IDENTITE</t>
+  </si>
+  <si>
+    <t>Copie pièce d'identité</t>
+  </si>
+  <si>
+    <t>EXPPAT_3</t>
+  </si>
+  <si>
+    <t>Directives anticipées</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
 </sst>
 </file>
@@ -453,7 +457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -553,47 +557,85 @@
         <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B13" t="s" s="2">
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>51</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
+      <c r="B2" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B14" t="s" s="2">
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>53</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
+      <c r="B3" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B15" t="s" s="2">
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
         <v>55</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
+      <c r="B4" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B16" t="s" s="2">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B17" t="s" s="2">
+      <c r="B5" t="s" s="2">
         <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-checklist-dlu-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-checklist-dlu-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260916095455</t>
+    <t>20260928134052</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:54:55+01:00</t>
+    <t>2026-09-28T13:40:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
